--- a/docs/Logic Requirements/Ageipelago Alaric.xlsx
+++ b/docs/Logic Requirements/Ageipelago Alaric.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb6dd295c338e39f/Desktop/Logic Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{5B78E94A-1732-4CCE-BA09-21EF8EA8AEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD6AAE6-B730-486F-8294-FCCEF8A832C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2707DB3-40A1-4E53-8B3C-87923A909351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Alaric" sheetId="1" r:id="rId1"/>
+    <sheet name="The Battle of the Frigidus" sheetId="2" r:id="rId2"/>
+    <sheet name="Razing Hellas" sheetId="3" r:id="rId3"/>
+    <sheet name="The Belly of the Beast" sheetId="4" r:id="rId4"/>
+    <sheet name="The Giant Falls" sheetId="5" r:id="rId5"/>
+    <sheet name="A Kingdom of Our Own" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="176">
   <si>
     <t>Scenario</t>
   </si>
@@ -1587,81 +1592,6 @@
       <t xml:space="preserve">
 Identical to Moderate
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-12 Pikemen
-15 Elite Skirmishers
-6 Knights
-3 Mangonels
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-12 Pikemen
-15 Elite Skirmishers
-3 Mangonels
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Hard: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Identical to Moderate</t>
     </r>
   </si>
   <si>
@@ -2958,6 +2888,438 @@
       <t xml:space="preserve">
 Identical to Moderate</t>
     </r>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Requires Transport Ship</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <t>Elite Skirmisher</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Ibex</t>
+  </si>
+  <si>
+    <t>Brown Bear</t>
+  </si>
+  <si>
+    <t>Centurion</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Cataphract</t>
+  </si>
+  <si>
+    <t>Tarkan</t>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumber Camp   </t>
+  </si>
+  <si>
+    <t>Palisade Gate</t>
+  </si>
+  <si>
+    <t>Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Fishing Boat</t>
+  </si>
+  <si>
+    <t>No good way to kill these.</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mangonel
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Two-Handed</t>
+  </si>
+  <si>
+    <t>Huskarl</t>
+  </si>
+  <si>
+    <t>Elite Huskarl</t>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Dromon</t>
+  </si>
+  <si>
+    <t>Legionary</t>
+  </si>
+  <si>
+    <t>Elite Centurion</t>
+  </si>
+  <si>
+    <t>Siege Onager</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Emperor Honorius</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Despawns in Vanilla)</t>
+    </r>
+  </si>
+  <si>
+    <t>See Wall</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+12 Pikemen
+15 Elite Skirmishers
+6 Knights
+3 Mangonels
+3 War Galleys
+2 War Hulks
+2 Fire Ships (Only if Player has Dromons)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+12 Pikemen
+15 Elite Skirmishers
+3 Mangonels
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Hard: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+12 Pikemen
+15 Elite Skirmishers
+6 Knights
+3 Mangonels
+5 War Galleys
+3 War Hulks
+4 Fire Ships (Only if Player has Dromons)</t>
+    </r>
+  </si>
+  <si>
+    <t>War Hulk</t>
+  </si>
+  <si>
+    <t>Fire Ship</t>
+  </si>
+  <si>
+    <t>Requires Dromon</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Imperial Tower</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Amphitheatre</t>
+  </si>
+  <si>
+    <t>Goat</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Ataulf</t>
+  </si>
+  <si>
+    <t>Aqueduct</t>
+  </si>
+  <si>
+    <t>Colosseum</t>
+  </si>
+  <si>
+    <t>Arch of Constantine</t>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Elite Throwing Axeman</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Onager
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Heavy Scorpion
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Sarus</t>
+  </si>
+  <si>
+    <t>Sea Wall</t>
+  </si>
+  <si>
+    <t>Sea Gate</t>
   </si>
 </sst>
 </file>
@@ -3106,7 +3468,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3194,11 +3556,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3234,6 +3644,69 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3724,7 +4197,7 @@
         <v>47</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>48</v>
@@ -3735,27 +4208,27 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>49</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -3763,36 +4236,36 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="N7" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
@@ -3805,39 +4278,39 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="408.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3862,4 +4335,2295 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9316089-FB11-4993-993E-327A61138A4D}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K21" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="31"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78454FB7-193A-4E5E-9FFF-F84E82675620}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="K16" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="K17" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="K18" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="K19" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="K20" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="K21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="K22" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="K23" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="K24" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="K25" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="K26" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84100C08-004F-4D07-9790-4EE90877B6D9}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G35" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF2336-96D8-438B-9597-9B2CCB1DB7A5}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="K26" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="K27" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDD0A3DC-2031-4632-A032-6BBB6F614813}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G24" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K29" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+    </row>
+    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G31" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G32" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/Logic Requirements/Ageipelago Alaric.xlsx
+++ b/docs/Logic Requirements/Ageipelago Alaric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2707DB3-40A1-4E53-8B3C-87923A909351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BCAB41-9773-464E-9C60-D333312FDC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="175">
   <si>
     <t>Scenario</t>
   </si>
@@ -3099,9 +3099,6 @@
     <t>Man-at-Arms</t>
   </si>
   <si>
-    <t>Two-Handed</t>
-  </si>
-  <si>
     <t>Huskarl</t>
   </si>
   <si>
@@ -3127,27 +3124,6 @@
   </si>
   <si>
     <t>Siege Onager</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Emperor Honorius</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-(Despawns in Vanilla)</t>
-    </r>
   </si>
   <si>
     <t>See Wall</t>
@@ -3321,12 +3297,34 @@
   <si>
     <t>Sea Gate</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Emperor Honorius</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(Despawns in Vanilla)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3458,6 +3456,41 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2FE2F5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3608,7 +3641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3703,10 +3736,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4214,7 +4265,7 @@
         <v>49</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>50</v>
@@ -4418,7 +4469,7 @@
       </c>
     </row>
     <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="33" t="s">
         <v>124</v>
       </c>
       <c r="H7" s="8" t="s">
@@ -4578,7 +4629,7 @@
       <c r="H18" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="35" t="s">
         <v>134</v>
       </c>
       <c r="L18" s="8" t="s">
@@ -4600,7 +4651,7 @@
       </c>
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="34" t="s">
         <v>129</v>
       </c>
       <c r="H20" s="8" t="s">
@@ -5368,7 +5419,7 @@
       </c>
     </row>
     <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="35" t="s">
         <v>115</v>
       </c>
       <c r="H16" s="8" t="s">
@@ -5382,8 +5433,8 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="14" t="s">
-        <v>155</v>
+      <c r="G17" s="35" t="s">
+        <v>153</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>79</v>
@@ -5396,11 +5447,11 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="14" t="s">
-        <v>156</v>
+      <c r="G18" s="35" t="s">
+        <v>154</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>85</v>
@@ -5410,7 +5461,7 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="36" t="s">
         <v>141</v>
       </c>
       <c r="H19" s="8" t="s">
@@ -5423,9 +5474,9 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G20" s="19" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>79</v>
@@ -5439,7 +5490,7 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>79</v>
@@ -5459,7 +5510,7 @@
         <v>79</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>79</v>
@@ -5467,7 +5518,7 @@
     </row>
     <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G23" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>79</v>
@@ -5481,7 +5532,7 @@
     </row>
     <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G24" s="20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>79</v>
@@ -5495,7 +5546,7 @@
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>79</v>
@@ -5522,8 +5573,8 @@
       </c>
     </row>
     <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="15" t="s">
-        <v>147</v>
+      <c r="G27" s="34" t="s">
+        <v>146</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>113</v>
@@ -5536,8 +5587,8 @@
       </c>
     </row>
     <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="15" t="s">
-        <v>148</v>
+      <c r="G28" s="34" t="s">
+        <v>147</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>113</v>
@@ -5551,13 +5602,13 @@
     </row>
     <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K29" s="15" t="s">
-        <v>158</v>
+      <c r="K29" s="34" t="s">
+        <v>156</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>79</v>
@@ -5565,27 +5616,27 @@
     </row>
     <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="H31" s="8" t="s">
         <v>79</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>79</v>
@@ -5598,8 +5649,8 @@
       <c r="H32" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K32" s="21" t="s">
-        <v>161</v>
+      <c r="K32" s="39" t="s">
+        <v>159</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>79</v>
@@ -5627,7 +5678,7 @@
     </row>
     <row r="35" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="G35" s="9" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>79</v>
@@ -5709,7 +5760,7 @@
       <c r="H3" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="32" t="s">
         <v>114</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -5717,8 +5768,8 @@
       </c>
     </row>
     <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G4" s="9" t="s">
-        <v>162</v>
+      <c r="G4" s="33" t="s">
+        <v>160</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>79</v>
@@ -5732,7 +5783,7 @@
     </row>
     <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G5" s="20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>79</v>
@@ -5746,7 +5797,7 @@
     </row>
     <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G6" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>79</v>
@@ -5858,7 +5909,7 @@
     </row>
     <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G14" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>79</v>
@@ -5872,7 +5923,7 @@
     </row>
     <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G15" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>79</v>
@@ -5942,7 +5993,7 @@
     </row>
     <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G20" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>79</v>
@@ -5956,7 +6007,7 @@
     </row>
     <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G21" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>79</v>
@@ -5975,8 +6026,8 @@
       <c r="H22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K22" s="15" t="s">
-        <v>165</v>
+      <c r="K22" s="34" t="s">
+        <v>163</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>79</v>
@@ -5989,8 +6040,8 @@
       <c r="H23" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>166</v>
+      <c r="K23" s="34" t="s">
+        <v>164</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>79</v>
@@ -6003,22 +6054,22 @@
       <c r="H24" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>167</v>
+      <c r="K24" s="34" t="s">
+        <v>165</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="32" t="s">
-        <v>164</v>
+      <c r="G25" s="37" t="s">
+        <v>162</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>79</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>79</v>
@@ -6166,7 +6217,7 @@
       <c r="H3" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="32" t="s">
         <v>80</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -6258,7 +6309,7 @@
       </c>
     </row>
     <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="34" t="s">
         <v>118</v>
       </c>
       <c r="H10" s="8" t="s">
@@ -6272,8 +6323,8 @@
       </c>
     </row>
     <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G11" s="15" t="s">
-        <v>168</v>
+      <c r="G11" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>117</v>
@@ -6300,7 +6351,7 @@
       </c>
     </row>
     <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="34" t="s">
         <v>116</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -6356,8 +6407,8 @@
       </c>
     </row>
     <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="19" t="s">
-        <v>169</v>
+      <c r="G17" s="36" t="s">
+        <v>167</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>117</v>
@@ -6370,8 +6421,8 @@
       </c>
     </row>
     <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="19" t="s">
-        <v>163</v>
+      <c r="G18" s="36" t="s">
+        <v>161</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>117</v>
@@ -6384,8 +6435,8 @@
       </c>
     </row>
     <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="19" t="s">
-        <v>170</v>
+      <c r="G19" s="36" t="s">
+        <v>168</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>117</v>
@@ -6413,7 +6464,7 @@
     </row>
     <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G21" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>117</v>
@@ -6433,7 +6484,7 @@
         <v>117</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>117</v>
@@ -6446,8 +6497,8 @@
       <c r="H23" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>175</v>
+      <c r="K23" s="34" t="s">
+        <v>173</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>117</v>
@@ -6483,7 +6534,7 @@
     </row>
     <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>117</v>
@@ -6497,7 +6548,7 @@
     </row>
     <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>117</v>
@@ -6511,7 +6562,7 @@
     </row>
     <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G28" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>117</v>
@@ -6525,7 +6576,7 @@
     </row>
     <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G29" s="14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>117</v>
@@ -6539,7 +6590,7 @@
     </row>
     <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G30" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>117</v>
@@ -6549,7 +6600,7 @@
     </row>
     <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G31" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>117</v>
@@ -6558,8 +6609,8 @@
       <c r="L31" s="22"/>
     </row>
     <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G32" s="28" t="s">
-        <v>173</v>
+      <c r="G32" s="38" t="s">
+        <v>171</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>117</v>
